--- a/marketing/event list 1-Feb.xlsx
+++ b/marketing/event list 1-Feb.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Repositories\Melbourne-tech-guilds\marketing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4E3D1F1-AF9B-430B-AED9-F20930F0D889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4E479A-9AD2-408B-A17B-AEF77EF2CAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15345" xr2:uid="{9EBFCB59-C7FA-4087-958C-3843CC912522}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{9EBFCB59-C7FA-4087-958C-3843CC912522}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="84">
   <si>
     <t>Abhishek Godhani</t>
   </si>
@@ -253,13 +254,46 @@
   </si>
   <si>
     <t>AhmetSekerci</t>
+  </si>
+  <si>
+    <t>Aaron Baloc</t>
+  </si>
+  <si>
+    <t>aamirbaloch_123@yahoo.com</t>
+  </si>
+  <si>
+    <t>Chase Lien</t>
+  </si>
+  <si>
+    <t>chaseweilien.de@gmail.com</t>
+  </si>
+  <si>
+    <t>Fareed (Fareed)</t>
+  </si>
+  <si>
+    <t>fareed1983@gmail.com</t>
+  </si>
+  <si>
+    <t>Photo and Video Release</t>
+  </si>
+  <si>
+    <t>Opt-in</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>Opt-out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As desdribed in out Guild Charter Version 2.0 – January 2026 melbourne.techguilds.au you must opt in/out </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,8 +307,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF525252"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Wingdings"/>
+      <charset val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,8 +345,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F1F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -323,23 +375,111 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFE0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,6 +495,1847 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX10.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX11.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX12.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX13.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX14.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX15.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX16.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX17.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX18.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX19.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX2.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX20.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX21.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX22.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX23.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX24.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX25.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX26.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX27.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX28.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX29.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX3.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX30.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX31.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX32.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX33.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX34.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX4.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX5.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX6.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX7.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX8.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/activeX/activeX9.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{5512D116-5CC6-11CF-8D67-00AA00BDCE1D}" ax:persistence="persistStream" r:id="rId1"/>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1025" name="Control 1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1025"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCE97C26-B743-0594-D732-69D8D76240CE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1026" name="Control 2" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1026"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD4CB501-4C41-108E-C56E-126FF4294A84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1027" name="Control 3" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1027"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{705018DA-5633-88C2-606F-C2ECB52E304A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1028" name="Control 4" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1028"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85E23992-D061-F705-2DB6-8D717D11D732}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1029" name="Control 5" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1029"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0B235FE-1938-DA94-DBC4-F2EEF098AF1C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1030" name="Control 6" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1030"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE0C267B-3E67-CAF3-4099-B73EFE3B0AAE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1031" name="Control 7" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1031"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB9916E7-9C63-53A4-70E7-DC63AE4E0A69}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1032" name="Control 8" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1032"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE2E58E7-F142-621B-E588-2FBB69E6AF6B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1033" name="Control 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1033"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2729F116-2A48-571E-77D4-DAF23ED912D7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1034" name="Control 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1034"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0803083A-FA83-C7ED-2F69-0D89676FC0EA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1035" name="Control 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1035"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9517243-A033-46F9-4C8D-3D8479EE0349}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1036" name="Control 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1036"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DB60FA5-F6E3-264F-5FCC-399F1E6AFC0B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1037" name="Control 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1037"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6FCCCAF-D31F-D89C-7CF1-EC77BDB6AD30}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1038" name="Control 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1038"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{001D71A3-DD4A-7D0D-7366-F1FCB5B21F6F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1039" name="Control 15" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1039"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BF317DF-2BFA-CCB7-ECE3-B0B3832F8E9C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1040" name="Control 16" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1040"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9B6E864-E976-053C-C776-213D18E14791}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1041" name="Control 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1041"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{008DCE55-36B5-5957-08FD-82E776B93D0F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1042" name="Control 18" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1042"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C2BD00B-282D-85EF-52E7-7C2BEB322759}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1043" name="Control 19" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1043"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B900E9-78F4-6942-FEB0-B81DC6BDB138}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1044" name="Control 20" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1044"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A21EE07-0AC2-8CBA-78B3-71F76B82D47E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1045" name="Control 21" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1045"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57961BC2-6A50-2243-83B3-7CF0CF2068AD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1046" name="Control 22" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1046"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BB18626-1D71-A24A-59DF-7822518B8EAA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1047" name="Control 23" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1047"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBAF16A4-3989-8D58-6BCD-CB33CFEE5D6E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1048" name="Control 24" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1048"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7FEEB9B-0AFA-5AEE-BA48-F9FA670ACF01}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1049" name="Control 25" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1049"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8983408-1934-4E04-42DF-F10114073810}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1050" name="Control 26" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1050"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BC98870-628F-3E32-1E35-5A2EEE7D5E84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1051" name="Control 27" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1051"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD585EB3-843A-4820-F759-0DAEBD6C3DAC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1052" name="Control 28" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1052"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C538A5DA-F0E2-F579-7C9C-202A857052B5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1053" name="Control 29" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1053"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94762E9A-B2F1-9837-A933-2D9107B15E95}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>31</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1054" name="Control 30" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1054"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A620F5A-9B89-2BBB-EB73-EBE5CE1A4906}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1055" name="Control 31" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1055"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E9A5196-E5E3-4131-0B13-A03E73C688DB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1056" name="Control 32" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1056"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{287C3253-882B-D785-1F5F-D9C5B75E310C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>38100</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1057" name="Control 33" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1057"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95106383-EBF2-CCEB-225C-0F44B653630C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>257175</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>47625</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1058" name="Control 34" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1058"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B753EC41-8952-1138-A4F5-F0DA63917A91}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -657,458 +2638,2178 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A2:I47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="4" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D2" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="C20" s="13"/>
+      <c r="D20" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="C21" s="13"/>
+      <c r="D21" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="C25" s="13"/>
+      <c r="D25" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="C27" s="13"/>
+      <c r="D27" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="C28" s="13"/>
+      <c r="D28" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="C29" s="13"/>
+      <c r="D29" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="C30" s="13"/>
+      <c r="D30" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="C31" s="13"/>
+      <c r="D31" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="C35" s="13"/>
+      <c r="D35" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="15"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H38" s="15"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="15"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" s="15"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H41" s="15"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" s="15"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" s="15"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>69</v>
       </c>
     </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D2:G2"/>
+  </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="76" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="71" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8CF7D49-93E3-439A-96EA-A509E862DE9D}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="5"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7"/>
+      <c r="B23" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
+      <c r="B24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7"/>
+      <c r="B25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7"/>
+      <c r="B27" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7"/>
+      <c r="B29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7"/>
+      <c r="B30" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7"/>
+      <c r="B32" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7"/>
+      <c r="B35" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="B36" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1058" r:id="rId4" name="Control 34">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>36</xdr:row>
+                <xdr:rowOff>47625</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1058" r:id="rId4" name="Control 34"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1057" r:id="rId6" name="Control 33">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1057" r:id="rId6" name="Control 33"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1056" r:id="rId7" name="Control 32">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1056" r:id="rId7" name="Control 32"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1055" r:id="rId8" name="Control 31">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1055" r:id="rId8" name="Control 31"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1054" r:id="rId9" name="Control 30">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1054" r:id="rId9" name="Control 30"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1053" r:id="rId10" name="Control 29">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>31</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1053" r:id="rId10" name="Control 29"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1052" r:id="rId11" name="Control 28">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1052" r:id="rId11" name="Control 28"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1051" r:id="rId12" name="Control 27">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1051" r:id="rId12" name="Control 27"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1050" r:id="rId13" name="Control 26">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1050" r:id="rId13" name="Control 26"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1049" r:id="rId14" name="Control 25">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>26</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1049" r:id="rId14" name="Control 25"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1048" r:id="rId15" name="Control 24">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>26</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1048" r:id="rId15" name="Control 24"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1047" r:id="rId16" name="Control 23">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1047" r:id="rId16" name="Control 23"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1046" r:id="rId17" name="Control 22">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>24</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1046" r:id="rId17" name="Control 22"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1045" r:id="rId18" name="Control 21">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>23</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1045" r:id="rId18" name="Control 21"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1044" r:id="rId19" name="Control 20">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1044" r:id="rId19" name="Control 20"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1043" r:id="rId20" name="Control 19">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>21</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1043" r:id="rId20" name="Control 19"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1042" r:id="rId21" name="Control 18">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1042" r:id="rId21" name="Control 18"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1041" r:id="rId22" name="Control 17">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1041" r:id="rId22" name="Control 17"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1040" r:id="rId23" name="Control 16">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1040" r:id="rId23" name="Control 16"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1039" r:id="rId24" name="Control 15">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1039" r:id="rId24" name="Control 15"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1038" r:id="rId25" name="Control 14">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1038" r:id="rId25" name="Control 14"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1037" r:id="rId26" name="Control 13">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1037" r:id="rId26" name="Control 13"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1036" r:id="rId27" name="Control 12">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1036" r:id="rId27" name="Control 12"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1035" r:id="rId28" name="Control 11">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1035" r:id="rId28" name="Control 11"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1034" r:id="rId29" name="Control 10">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1034" r:id="rId29" name="Control 10"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1033" r:id="rId30" name="Control 9">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1033" r:id="rId30" name="Control 9"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1032" r:id="rId31" name="Control 8">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1032" r:id="rId31" name="Control 8"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1031" r:id="rId32" name="Control 7">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1031" r:id="rId32" name="Control 7"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1030" r:id="rId33" name="Control 6">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1030" r:id="rId33" name="Control 6"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1029" r:id="rId34" name="Control 5">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1029" r:id="rId34" name="Control 5"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1028" r:id="rId35" name="Control 4">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1028" r:id="rId35" name="Control 4"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1027" r:id="rId36" name="Control 3">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1027" r:id="rId36" name="Control 3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1026" r:id="rId37" name="Control 2">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1026" r:id="rId37" name="Control 2"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="1025" r:id="rId38" name="Control 1">
+          <controlPr defaultSize="0" r:id="rId5">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>257175</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>38100</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="1025" r:id="rId38" name="Control 1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
 </worksheet>
 </file>